--- a/artfynd/A 9522-2023 artfynd.xlsx
+++ b/artfynd/A 9522-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 9522-2023 artfynd.xlsx
+++ b/artfynd/A 9522-2023 artfynd.xlsx
@@ -2066,7 +2066,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121062613</v>
+        <v>121062614</v>
       </c>
       <c r="B12" t="n">
         <v>42961</v>
@@ -2101,7 +2101,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -2123,10 +2123,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>690350</v>
+        <v>690348</v>
       </c>
       <c r="R12" t="n">
-        <v>6661448</v>
+        <v>6661447</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2163,7 +2163,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>2 m upp.</t>
+          <t>2 m upp. Stor olvonbuske</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2210,7 +2210,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121062614</v>
+        <v>121062613</v>
       </c>
       <c r="B13" t="n">
         <v>42961</v>
@@ -2245,7 +2245,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2267,10 +2267,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>690348</v>
+        <v>690350</v>
       </c>
       <c r="R13" t="n">
-        <v>6661447</v>
+        <v>6661448</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2307,7 +2307,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>2 m upp. Stor olvonbuske</t>
+          <t>2 m upp.</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 9522-2023 artfynd.xlsx
+++ b/artfynd/A 9522-2023 artfynd.xlsx
@@ -2066,7 +2066,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121062614</v>
+        <v>121062613</v>
       </c>
       <c r="B12" t="n">
         <v>42961</v>
@@ -2101,7 +2101,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -2123,10 +2123,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>690348</v>
+        <v>690350</v>
       </c>
       <c r="R12" t="n">
-        <v>6661447</v>
+        <v>6661448</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2163,7 +2163,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>2 m upp. Stor olvonbuske</t>
+          <t>2 m upp.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2210,7 +2210,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121062613</v>
+        <v>121062614</v>
       </c>
       <c r="B13" t="n">
         <v>42961</v>
@@ -2245,7 +2245,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2267,10 +2267,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>690350</v>
+        <v>690348</v>
       </c>
       <c r="R13" t="n">
-        <v>6661448</v>
+        <v>6661447</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2307,7 +2307,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>2 m upp.</t>
+          <t>2 m upp. Stor olvonbuske</t>
         </is>
       </c>
       <c r="AD13" t="b">
